--- a/artfynd/A 15941-2024 artfynd.xlsx
+++ b/artfynd/A 15941-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>117305337</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117305536</v>
+        <v>117305439</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585683</v>
+        <v>585659</v>
       </c>
       <c r="R3" t="n">
-        <v>6325869</v>
+        <v>6325863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -908,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117305439</v>
+        <v>117305536</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -964,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585659</v>
+        <v>585683</v>
       </c>
       <c r="R4" t="n">
-        <v>6325863</v>
+        <v>6325869</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117305624</v>
+        <v>117305576</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585715</v>
+        <v>585679</v>
       </c>
       <c r="R5" t="n">
-        <v>6325781</v>
+        <v>6325772</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1146,15 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117305576</v>
+        <v>117305624</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1156,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1202,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585679</v>
+        <v>585715</v>
       </c>
       <c r="R6" t="n">
-        <v>6325772</v>
+        <v>6325781</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 15941-2024 artfynd.xlsx
+++ b/artfynd/A 15941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305536</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305576</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117305624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>